--- a/data/google_news_dedup_audit_30_0326_UTC.xlsx
+++ b/data/google_news_dedup_audit_30_0326_UTC.xlsx
@@ -413,58 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>kept_original_row</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>dropped_original_row</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>similarity</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>kept_title</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dropped_title</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9031791687011719</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Stroomstoring in Kerkveld in Lanaken opgelost - hln.be</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Stroomstoring in Kerkveld in Lanaken opgelost | Foto - hln.be</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>